--- a/数据/示例_JSON步骤.xlsx
+++ b/数据/示例_JSON步骤.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
   <si>
     <t>测试用例名称</t>
   </si>
@@ -78,12 +78,6 @@
   "result": "ok",
   "code": 0
 }</t>
-  </si>
-  <si>
-    <t>查询_003</t>
-  </si>
-  <si>
-    <t>CSH-LT_GN-003</t>
   </si>
   <si>
     <t>{
@@ -1122,19 +1116,19 @@
     </row>
     <row r="4" ht="72" spans="1:5">
       <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
